--- a/tabelas/2020.xlsx
+++ b/tabelas/2020.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\narrativapilotodois-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24A52686-90A5-4A9E-9BC1-8C426CFC17ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA022905-9995-41AC-9413-E65977589E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{349979B7-C21B-407A-A293-DC1F6033EF36}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="209">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -652,9 +652,6 @@
   </si>
   <si>
     <t>08.779.141.0024.001</t>
-  </si>
-  <si>
-    <t>08.779.141.0180.000</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEC8DEA-D1AE-4B91-B66D-48CA0A2026FB}">
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -5107,40 +5104,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G125" s="2">
-        <v>2020</v>
-      </c>
-      <c r="H125" s="2">
-        <v>0</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J125" t="s">
-        <v>29</v>
-      </c>
-      <c r="K125" t="s">
-        <v>31</v>
-      </c>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
